--- a/output/2026-10-01_22_Malesia_Melaka_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-01_22_Malesia_Melaka_Depolverazione_Trattamento_aria.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Produttore/fornitore confermato: dust collector portatili (serie CA), unità JetcleanDF a cartuccia, spray booth, ventilatori centrifughi. Sede a Kajang, Selangor; non a Melaka ma copertura nazionale.</t>
+          <t>Produttore/fornitore confermato: dust collector portatili (serie CA), unità JetcleanDF a cartuccia, spray booth, ventilatori centrifughi. Sede a Kajang, Selangor; non a Melaka ma copertura nazionale. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Confermato: specialista controllo inquinamento aria (dust collector bag/cartridge, wet scrubber, spray booth, ducting), dal 2007. Sede a Shah Alam, Selangor; copertura nazionale.</t>
+          <t>Confermato: specialista controllo inquinamento aria (dust collector bag/cartridge, wet scrubber, spray booth, ducting), dal 2007. Sede a Shah Alam, Selangor; copertura nazionale. [DUPLICATO — vedi anche: 2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Confermato: produttore dust collector (bag filter, cartridge, multi-cyclone, wet scrubber), blower fan, trasporto pneumatico, dal 2002. Sede a Shah Alam, Selangor; copertura nazionale.</t>
+          <t>Confermato: produttore dust collector (bag filter, cartridge, multi-cyclone, wet scrubber), blower fan, trasporto pneumatico, dal 2002. Sede a Shah Alam, Selangor; copertura nazionale. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Confermato: pagina dedicata sul sito 'Dust Collector Supplier In Johor' che dichiara copertura di Johor Bahru, Kuala Lumpur e Melaka. Sede a Senai, Johor.</t>
+          <t>Confermato: pagina dedicata sul sito 'Dust Collector Supplier In Johor' che dichiara copertura di Johor Bahru, Kuala Lumpur e Melaka. Sede a Senai, Johor. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -736,7 +736,6 @@
           <t>+6012-792 2192</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Confermato: fornitore dust/fume/mist collector ad alte prestazioni, distributore Donaldson Industrial Air Filtration. Sede principale Johor Bahru, Johor; sede secondaria Pelabuhan Klang, Selangor. Email generica presente sul sito ma oscurata/non estraibile in modo affidabile, lasciata vuota.</t>
@@ -744,7 +743,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -781,7 +780,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Confermato tramite fetch pagina 'about': fornitore specializzato dust collector con 37 anni di esperienza. Sedi a Ara Damansara e Subang Jaya, fabbrica a Puchong, Selangor. Non a Melaka ma copertura nazionale.</t>
+          <t>Confermato tramite fetch pagina 'about': fornitore specializzato dust collector con 37 anni di esperienza. Sedi a Ara Damansara e Subang Jaya, fabbrica a Puchong, Selangor. Non a Melaka ma copertura nazionale. [DUPLICATO — vedi anche: 2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -823,7 +822,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Confermato: produttore/fornitore filtri industriali (filter bag, cage, cartridge) e dust collector portatili, oltre 25 anni di esperienza. Sede a Shah Alam, Selangor.</t>
+          <t>Confermato: produttore/fornitore filtri industriali (filter bag, cage, cartridge) e dust collector portatili, oltre 25 anni di esperienza. Sede a Shah Alam, Selangor. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -858,7 +857,6 @@
           <t>03-5880 4179</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Confermato: produttore filtri per dust collector (cartucce, sacchi) e filtri AHU/HEPA per AHU, dal 1998, ISO 9001:2015. Sede a Subang Jaya, Selangor. Email generica non reperita con fonte certa.</t>
@@ -866,7 +864,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -950,7 +948,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-01_22_Malesia_Melaka_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-01_22_Malesia_Melaka_Depolverazione_Trattamento_aria.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore industriale multibrand (MRO) con sede fisica a Melaka. Confermato tramite sito e ricerca: distribuisce dust collector HITZ e JETMAC e estrattori fumi di saldatura PLYMOVENT GOLINE. Candidato forte.</t>
+          <t>Distributore industriale multibrand (MRO) con sede fisica a Melaka. Confermato tramite sito e ricerca: distribuisce dust collector HITZ e JETMAC e estrattori fumi di saldatura PLYMOVENT GOLINE. Candidato forte. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Confermato: fornitore dust/fume/mist collector ad alte prestazioni, distributore Donaldson Industrial Air Filtration. Sede principale Johor Bahru, Johor; sede secondaria Pelabuhan Klang, Selangor. Email generica presente sul sito ma oscurata/non estraibile in modo affidabile, lasciata vuota.</t>
+          <t>Confermato: fornitore dust/fume/mist collector ad alte prestazioni, distributore Donaldson Industrial Air Filtration. Sede principale Johor Bahru, Johor; sede secondaria Pelabuhan Klang, Selangor. Email generica presente sul sito ma oscurata/non estraibile in modo affidabile, lasciata vuota. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Confermato: produttore filtri per dust collector (cartucce, sacchi) e filtri AHU/HEPA per AHU, dal 1998, ISO 9001:2015. Sede a Subang Jaya, Selangor. Email generica non reperita con fonte certa.</t>
+          <t>Confermato: produttore filtri per dust collector (cartucce, sacchi) e filtri AHU/HEPA per AHU, dal 1998, ISO 9001:2015. Sede a Subang Jaya, Selangor. Email generica non reperita con fonte certa. [DUPLICATO — vedi anche: 2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Confermato: sussidiaria di Tanabe Engineering Corporation (Giappone) dal 2017, offre sistemi dust collector (bag, cartridge, wet) e ducting per il settore petrolchimico. Sede a Petaling Jaya, Selangor.</t>
+          <t>Confermato: sussidiaria di Tanabe Engineering Corporation (Giappone) dal 2017, offre sistemi dust collector (bag, cartridge, wet) e ducting per il settore petrolchimico. Sede a Petaling Jaya, Selangor. [DUPLICATO — vedi anche: 2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
